--- a/escola-de-obra/05-curso-concreto/kit/planilha/planilha-concreto.xlsx
+++ b/escola-de-obra/05-curso-concreto/kit/planilha/planilha-concreto.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Faixa da NBR 7212 conforme o slump pedido. [VALIDAR F4]</t>
+          <t>Faixa da NBR 7212:2021 conforme o slump pedido. [VALIDAR F4]</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Da adição da água ao fim da descarga (NBR 7212; aditivos podem alterar). [VALIDAR F2]</t>
+          <t>Da adição da água ao fim da descarga (NBR 7212:2021; aditivos podem alterar). [VALIDAR F2]</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>⚠ A aceitação definitiva do concreto segue os critérios estatísticos da NBR 12655 — a coluna 'situação' da aba CPs é uma triagem de alerta, não o critério final. [VALIDAR F7]</t>
+          <t>⚠ A aceitação definitiva do concreto segue os critérios estatísticos da NBR 12655:2022 — a coluna 'situação' da aba CPs é uma triagem de alerta, não o critério final. [VALIDAR F7]</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECEBIMENTO — uma linha por caminhão (aceitação provisória, NBR 12655/7212/16889)</t>
+          <t>RECEBIMENTO — uma linha por caminhão (aceitação provisória, NBR 12655:2022/7212/16889)</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CORPOS DE PROVA — moldagem NBR 5738 · ensaio NBR 5739 · aceitação NBR 12655</t>
+          <t>CORPOS DE PROVA — moldagem NBR 5738:2015 · ensaio NBR 5739:2018 · aceitação NBR 12655:2022</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="16" t="n"/>
       <c r="G3" s="9">
-        <f>IF(F3="","",IF(F3&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F3="","",IF(F3&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H3" s="11" t="n"/>
@@ -2930,7 +2930,7 @@
       <c r="E4" s="13" t="n"/>
       <c r="F4" s="17" t="n"/>
       <c r="G4" s="13">
-        <f>IF(F4="","",IF(F4&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F4="","",IF(F4&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H4" s="15" t="n"/>
@@ -2943,7 +2943,7 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="16" t="n"/>
       <c r="G5" s="9">
-        <f>IF(F5="","",IF(F5&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F5="","",IF(F5&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H5" s="11" t="n"/>
@@ -2956,7 +2956,7 @@
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="13">
-        <f>IF(F6="","",IF(F6&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F6="","",IF(F6&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H6" s="15" t="n"/>
@@ -2969,7 +2969,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="16" t="n"/>
       <c r="G7" s="9">
-        <f>IF(F7="","",IF(F7&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F7="","",IF(F7&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H7" s="11" t="n"/>
@@ -2982,7 +2982,7 @@
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="13">
-        <f>IF(F8="","",IF(F8&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F8="","",IF(F8&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H8" s="15" t="n"/>
@@ -2995,7 +2995,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="16" t="n"/>
       <c r="G9" s="9">
-        <f>IF(F9="","",IF(F9&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F9="","",IF(F9&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H9" s="11" t="n"/>
@@ -3008,7 +3008,7 @@
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="13">
-        <f>IF(F10="","",IF(F10&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F10="","",IF(F10&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H10" s="15" t="n"/>
@@ -3021,7 +3021,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="9">
-        <f>IF(F11="","",IF(F11&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F11="","",IF(F11&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H11" s="11" t="n"/>
@@ -3034,7 +3034,7 @@
       <c r="E12" s="13" t="n"/>
       <c r="F12" s="17" t="n"/>
       <c r="G12" s="13">
-        <f>IF(F12="","",IF(F12&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F12="","",IF(F12&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H12" s="15" t="n"/>
@@ -3047,7 +3047,7 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="9">
-        <f>IF(F13="","",IF(F13&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F13="","",IF(F13&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H13" s="11" t="n"/>
@@ -3060,7 +3060,7 @@
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="17" t="n"/>
       <c r="G14" s="13">
-        <f>IF(F14="","",IF(F14&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F14="","",IF(F14&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H14" s="15" t="n"/>
@@ -3073,7 +3073,7 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="9">
-        <f>IF(F15="","",IF(F15&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F15="","",IF(F15&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -3086,7 +3086,7 @@
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="17" t="n"/>
       <c r="G16" s="13">
-        <f>IF(F16="","",IF(F16&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F16="","",IF(F16&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H16" s="15" t="n"/>
@@ -3099,7 +3099,7 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="9">
-        <f>IF(F17="","",IF(F17&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F17="","",IF(F17&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H17" s="11" t="n"/>
@@ -3112,7 +3112,7 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="13">
-        <f>IF(F18="","",IF(F18&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F18="","",IF(F18&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H18" s="15" t="n"/>
@@ -3125,7 +3125,7 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="16" t="n"/>
       <c r="G19" s="9">
-        <f>IF(F19="","",IF(F19&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F19="","",IF(F19&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H19" s="11" t="n"/>
@@ -3138,7 +3138,7 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="17" t="n"/>
       <c r="G20" s="13">
-        <f>IF(F20="","",IF(F20&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F20="","",IF(F20&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H20" s="15" t="n"/>
@@ -3151,7 +3151,7 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="9">
-        <f>IF(F21="","",IF(F21&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F21="","",IF(F21&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H21" s="11" t="n"/>
@@ -3164,7 +3164,7 @@
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="17" t="n"/>
       <c r="G22" s="13">
-        <f>IF(F22="","",IF(F22&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F22="","",IF(F22&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H22" s="15" t="n"/>
@@ -3177,7 +3177,7 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="9">
-        <f>IF(F23="","",IF(F23&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F23="","",IF(F23&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H23" s="11" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="E24" s="13" t="n"/>
       <c r="F24" s="17" t="n"/>
       <c r="G24" s="13">
-        <f>IF(F24="","",IF(F24&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F24="","",IF(F24&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H24" s="15" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="16" t="n"/>
       <c r="G25" s="9">
-        <f>IF(F25="","",IF(F25&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F25="","",IF(F25&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H25" s="11" t="n"/>
@@ -3216,7 +3216,7 @@
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="13">
-        <f>IF(F26="","",IF(F26&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F26="","",IF(F26&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H26" s="15" t="n"/>
@@ -3229,7 +3229,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="16" t="n"/>
       <c r="G27" s="9">
-        <f>IF(F27="","",IF(F27&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F27="","",IF(F27&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H27" s="11" t="n"/>
@@ -3242,7 +3242,7 @@
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="17" t="n"/>
       <c r="G28" s="13">
-        <f>IF(F28="","",IF(F28&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F28="","",IF(F28&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H28" s="15" t="n"/>
@@ -3255,7 +3255,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="16" t="n"/>
       <c r="G29" s="9">
-        <f>IF(F29="","",IF(F29&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F29="","",IF(F29&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H29" s="11" t="n"/>
@@ -3268,7 +3268,7 @@
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="13">
-        <f>IF(F30="","",IF(F30&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F30="","",IF(F30&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H30" s="15" t="n"/>
@@ -3281,7 +3281,7 @@
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="16" t="n"/>
       <c r="G31" s="9">
-        <f>IF(F31="","",IF(F31&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F31="","",IF(F31&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H31" s="11" t="n"/>
@@ -3294,7 +3294,7 @@
       <c r="E32" s="13" t="n"/>
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="13">
-        <f>IF(F32="","",IF(F32&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F32="","",IF(F32&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H32" s="15" t="n"/>
@@ -3307,7 +3307,7 @@
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="9">
-        <f>IF(F33="","",IF(F33&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F33="","",IF(F33&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H33" s="11" t="n"/>
@@ -3320,7 +3320,7 @@
       <c r="E34" s="13" t="n"/>
       <c r="F34" s="17" t="n"/>
       <c r="G34" s="13">
-        <f>IF(F34="","",IF(F34&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F34="","",IF(F34&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H34" s="15" t="n"/>
@@ -3333,7 +3333,7 @@
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="16" t="n"/>
       <c r="G35" s="9">
-        <f>IF(F35="","",IF(F35&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F35="","",IF(F35&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H35" s="11" t="n"/>
@@ -3346,7 +3346,7 @@
       <c r="E36" s="13" t="n"/>
       <c r="F36" s="17" t="n"/>
       <c r="G36" s="13">
-        <f>IF(F36="","",IF(F36&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F36="","",IF(F36&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H36" s="15" t="n"/>
@@ -3359,7 +3359,7 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="16" t="n"/>
       <c r="G37" s="9">
-        <f>IF(F37="","",IF(F37&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F37="","",IF(F37&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H37" s="11" t="n"/>
@@ -3372,7 +3372,7 @@
       <c r="E38" s="13" t="n"/>
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="13">
-        <f>IF(F38="","",IF(F38&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F38="","",IF(F38&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H38" s="15" t="n"/>
@@ -3385,7 +3385,7 @@
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="9">
-        <f>IF(F39="","",IF(F39&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F39="","",IF(F39&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H39" s="11" t="n"/>
@@ -3398,7 +3398,7 @@
       <c r="E40" s="13" t="n"/>
       <c r="F40" s="17" t="n"/>
       <c r="G40" s="13">
-        <f>IF(F40="","",IF(F40&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F40="","",IF(F40&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H40" s="15" t="n"/>
@@ -3411,7 +3411,7 @@
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="16" t="n"/>
       <c r="G41" s="9">
-        <f>IF(F41="","",IF(F41&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F41="","",IF(F41&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H41" s="11" t="n"/>
@@ -3424,7 +3424,7 @@
       <c r="E42" s="13" t="n"/>
       <c r="F42" s="17" t="n"/>
       <c r="G42" s="13">
-        <f>IF(F42="","",IF(F42&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F42="","",IF(F42&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H42" s="15" t="n"/>
@@ -3437,7 +3437,7 @@
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="16" t="n"/>
       <c r="G43" s="9">
-        <f>IF(F43="","",IF(F43&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F43="","",IF(F43&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H43" s="11" t="n"/>
@@ -3450,7 +3450,7 @@
       <c r="E44" s="13" t="n"/>
       <c r="F44" s="17" t="n"/>
       <c r="G44" s="13">
-        <f>IF(F44="","",IF(F44&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F44="","",IF(F44&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H44" s="15" t="n"/>
@@ -3463,7 +3463,7 @@
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="16" t="n"/>
       <c r="G45" s="9">
-        <f>IF(F45="","",IF(F45&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F45="","",IF(F45&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H45" s="11" t="n"/>
@@ -3476,7 +3476,7 @@
       <c r="E46" s="13" t="n"/>
       <c r="F46" s="17" t="n"/>
       <c r="G46" s="13">
-        <f>IF(F46="","",IF(F46&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F46="","",IF(F46&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H46" s="15" t="n"/>
@@ -3489,7 +3489,7 @@
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="16" t="n"/>
       <c r="G47" s="9">
-        <f>IF(F47="","",IF(F47&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F47="","",IF(F47&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H47" s="11" t="n"/>
@@ -3502,7 +3502,7 @@
       <c r="E48" s="13" t="n"/>
       <c r="F48" s="17" t="n"/>
       <c r="G48" s="13">
-        <f>IF(F48="","",IF(F48&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F48="","",IF(F48&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H48" s="15" t="n"/>
@@ -3515,7 +3515,7 @@
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="16" t="n"/>
       <c r="G49" s="9">
-        <f>IF(F49="","",IF(F49&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F49="","",IF(F49&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H49" s="11" t="n"/>
@@ -3528,7 +3528,7 @@
       <c r="E50" s="13" t="n"/>
       <c r="F50" s="17" t="n"/>
       <c r="G50" s="13">
-        <f>IF(F50="","",IF(F50&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F50="","",IF(F50&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H50" s="15" t="n"/>
@@ -3541,7 +3541,7 @@
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="16" t="n"/>
       <c r="G51" s="9">
-        <f>IF(F51="","",IF(F51&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F51="","",IF(F51&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H51" s="11" t="n"/>
@@ -3554,7 +3554,7 @@
       <c r="E52" s="13" t="n"/>
       <c r="F52" s="17" t="n"/>
       <c r="G52" s="13">
-        <f>IF(F52="","",IF(F52&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F52="","",IF(F52&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H52" s="15" t="n"/>
@@ -3567,7 +3567,7 @@
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="16" t="n"/>
       <c r="G53" s="9">
-        <f>IF(F53="","",IF(F53&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F53="","",IF(F53&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H53" s="11" t="n"/>
@@ -3580,7 +3580,7 @@
       <c r="E54" s="13" t="n"/>
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="13">
-        <f>IF(F54="","",IF(F54&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F54="","",IF(F54&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H54" s="15" t="n"/>
@@ -3593,7 +3593,7 @@
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="16" t="n"/>
       <c r="G55" s="9">
-        <f>IF(F55="","",IF(F55&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F55="","",IF(F55&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H55" s="11" t="n"/>
@@ -3606,7 +3606,7 @@
       <c r="E56" s="13" t="n"/>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="13">
-        <f>IF(F56="","",IF(F56&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F56="","",IF(F56&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H56" s="15" t="n"/>
@@ -3619,7 +3619,7 @@
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="16" t="n"/>
       <c r="G57" s="9">
-        <f>IF(F57="","",IF(F57&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F57="","",IF(F57&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H57" s="11" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="E58" s="13" t="n"/>
       <c r="F58" s="17" t="n"/>
       <c r="G58" s="13">
-        <f>IF(F58="","",IF(F58&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F58="","",IF(F58&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H58" s="15" t="n"/>
@@ -3645,7 +3645,7 @@
       <c r="E59" s="9" t="n"/>
       <c r="F59" s="16" t="n"/>
       <c r="G59" s="9">
-        <f>IF(F59="","",IF(F59&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F59="","",IF(F59&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H59" s="11" t="n"/>
@@ -3658,7 +3658,7 @@
       <c r="E60" s="13" t="n"/>
       <c r="F60" s="17" t="n"/>
       <c r="G60" s="13">
-        <f>IF(F60="","",IF(F60&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F60="","",IF(F60&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H60" s="15" t="n"/>
@@ -3671,7 +3671,7 @@
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="16" t="n"/>
       <c r="G61" s="9">
-        <f>IF(F61="","",IF(F61&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F61="","",IF(F61&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H61" s="11" t="n"/>
@@ -3684,7 +3684,7 @@
       <c r="E62" s="13" t="n"/>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="13">
-        <f>IF(F62="","",IF(F62&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F62="","",IF(F62&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H62" s="15" t="n"/>
@@ -3697,7 +3697,7 @@
       <c r="E63" s="9" t="n"/>
       <c r="F63" s="16" t="n"/>
       <c r="G63" s="9">
-        <f>IF(F63="","",IF(F63&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F63="","",IF(F63&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H63" s="11" t="n"/>
@@ -3710,7 +3710,7 @@
       <c r="E64" s="13" t="n"/>
       <c r="F64" s="17" t="n"/>
       <c r="G64" s="13">
-        <f>IF(F64="","",IF(F64&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F64="","",IF(F64&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H64" s="15" t="n"/>
@@ -3723,7 +3723,7 @@
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="9">
-        <f>IF(F65="","",IF(F65&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F65="","",IF(F65&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H65" s="11" t="n"/>
@@ -3736,7 +3736,7 @@
       <c r="E66" s="13" t="n"/>
       <c r="F66" s="17" t="n"/>
       <c r="G66" s="13">
-        <f>IF(F66="","",IF(F66&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F66="","",IF(F66&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H66" s="15" t="n"/>
@@ -3749,7 +3749,7 @@
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="16" t="n"/>
       <c r="G67" s="9">
-        <f>IF(F67="","",IF(F67&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F67="","",IF(F67&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H67" s="11" t="n"/>
@@ -3762,7 +3762,7 @@
       <c r="E68" s="13" t="n"/>
       <c r="F68" s="17" t="n"/>
       <c r="G68" s="13">
-        <f>IF(F68="","",IF(F68&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F68="","",IF(F68&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H68" s="15" t="n"/>
@@ -3775,7 +3775,7 @@
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="16" t="n"/>
       <c r="G69" s="9">
-        <f>IF(F69="","",IF(F69&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F69="","",IF(F69&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H69" s="11" t="n"/>
@@ -3788,7 +3788,7 @@
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="17" t="n"/>
       <c r="G70" s="13">
-        <f>IF(F70="","",IF(F70&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F70="","",IF(F70&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H70" s="15" t="n"/>
@@ -3801,7 +3801,7 @@
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="16" t="n"/>
       <c r="G71" s="9">
-        <f>IF(F71="","",IF(F71&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F71="","",IF(F71&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H71" s="11" t="n"/>
@@ -3814,7 +3814,7 @@
       <c r="E72" s="13" t="n"/>
       <c r="F72" s="17" t="n"/>
       <c r="G72" s="13">
-        <f>IF(F72="","",IF(F72&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F72="","",IF(F72&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H72" s="15" t="n"/>
@@ -3827,7 +3827,7 @@
       <c r="E73" s="9" t="n"/>
       <c r="F73" s="16" t="n"/>
       <c r="G73" s="9">
-        <f>IF(F73="","",IF(F73&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F73="","",IF(F73&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H73" s="11" t="n"/>
@@ -3840,7 +3840,7 @@
       <c r="E74" s="13" t="n"/>
       <c r="F74" s="17" t="n"/>
       <c r="G74" s="13">
-        <f>IF(F74="","",IF(F74&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F74="","",IF(F74&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H74" s="15" t="n"/>
@@ -3853,7 +3853,7 @@
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="16" t="n"/>
       <c r="G75" s="9">
-        <f>IF(F75="","",IF(F75&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F75="","",IF(F75&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H75" s="11" t="n"/>
@@ -3866,7 +3866,7 @@
       <c r="E76" s="13" t="n"/>
       <c r="F76" s="17" t="n"/>
       <c r="G76" s="13">
-        <f>IF(F76="","",IF(F76&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F76="","",IF(F76&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H76" s="15" t="n"/>
@@ -3879,7 +3879,7 @@
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="16" t="n"/>
       <c r="G77" s="9">
-        <f>IF(F77="","",IF(F77&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F77="","",IF(F77&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H77" s="11" t="n"/>
@@ -3892,7 +3892,7 @@
       <c r="E78" s="13" t="n"/>
       <c r="F78" s="17" t="n"/>
       <c r="G78" s="13">
-        <f>IF(F78="","",IF(F78&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F78="","",IF(F78&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H78" s="15" t="n"/>
@@ -3905,7 +3905,7 @@
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="16" t="n"/>
       <c r="G79" s="9">
-        <f>IF(F79="","",IF(F79&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F79="","",IF(F79&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H79" s="11" t="n"/>
@@ -3918,7 +3918,7 @@
       <c r="E80" s="13" t="n"/>
       <c r="F80" s="17" t="n"/>
       <c r="G80" s="13">
-        <f>IF(F80="","",IF(F80&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F80="","",IF(F80&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H80" s="15" t="n"/>
@@ -3931,7 +3931,7 @@
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="16" t="n"/>
       <c r="G81" s="9">
-        <f>IF(F81="","",IF(F81&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F81="","",IF(F81&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H81" s="11" t="n"/>
@@ -3944,7 +3944,7 @@
       <c r="E82" s="13" t="n"/>
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="13">
-        <f>IF(F82="","",IF(F82&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F82="","",IF(F82&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H82" s="15" t="n"/>
@@ -3957,7 +3957,7 @@
       <c r="E83" s="9" t="n"/>
       <c r="F83" s="16" t="n"/>
       <c r="G83" s="9">
-        <f>IF(F83="","",IF(F83&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F83="","",IF(F83&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H83" s="11" t="n"/>
@@ -3970,7 +3970,7 @@
       <c r="E84" s="13" t="n"/>
       <c r="F84" s="17" t="n"/>
       <c r="G84" s="13">
-        <f>IF(F84="","",IF(F84&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F84="","",IF(F84&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H84" s="15" t="n"/>
@@ -3983,7 +3983,7 @@
       <c r="E85" s="9" t="n"/>
       <c r="F85" s="16" t="n"/>
       <c r="G85" s="9">
-        <f>IF(F85="","",IF(F85&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F85="","",IF(F85&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H85" s="11" t="n"/>
@@ -3996,7 +3996,7 @@
       <c r="E86" s="13" t="n"/>
       <c r="F86" s="17" t="n"/>
       <c r="G86" s="13">
-        <f>IF(F86="","",IF(F86&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F86="","",IF(F86&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H86" s="15" t="n"/>
@@ -4009,7 +4009,7 @@
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="16" t="n"/>
       <c r="G87" s="9">
-        <f>IF(F87="","",IF(F87&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F87="","",IF(F87&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H87" s="11" t="n"/>
@@ -4022,7 +4022,7 @@
       <c r="E88" s="13" t="n"/>
       <c r="F88" s="17" t="n"/>
       <c r="G88" s="13">
-        <f>IF(F88="","",IF(F88&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F88="","",IF(F88&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H88" s="15" t="n"/>
@@ -4035,7 +4035,7 @@
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="16" t="n"/>
       <c r="G89" s="9">
-        <f>IF(F89="","",IF(F89&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F89="","",IF(F89&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H89" s="11" t="n"/>
@@ -4048,7 +4048,7 @@
       <c r="E90" s="13" t="n"/>
       <c r="F90" s="17" t="n"/>
       <c r="G90" s="13">
-        <f>IF(F90="","",IF(F90&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F90="","",IF(F90&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H90" s="15" t="n"/>
@@ -4061,7 +4061,7 @@
       <c r="E91" s="9" t="n"/>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="9">
-        <f>IF(F91="","",IF(F91&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F91="","",IF(F91&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H91" s="11" t="n"/>
@@ -4074,7 +4074,7 @@
       <c r="E92" s="13" t="n"/>
       <c r="F92" s="17" t="n"/>
       <c r="G92" s="13">
-        <f>IF(F92="","",IF(F92&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F92="","",IF(F92&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H92" s="15" t="n"/>
@@ -4087,7 +4087,7 @@
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="16" t="n"/>
       <c r="G93" s="9">
-        <f>IF(F93="","",IF(F93&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F93="","",IF(F93&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H93" s="11" t="n"/>
@@ -4100,7 +4100,7 @@
       <c r="E94" s="13" t="n"/>
       <c r="F94" s="17" t="n"/>
       <c r="G94" s="13">
-        <f>IF(F94="","",IF(F94&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F94="","",IF(F94&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H94" s="15" t="n"/>
@@ -4113,7 +4113,7 @@
       <c r="E95" s="9" t="n"/>
       <c r="F95" s="16" t="n"/>
       <c r="G95" s="9">
-        <f>IF(F95="","",IF(F95&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F95="","",IF(F95&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H95" s="11" t="n"/>
@@ -4126,7 +4126,7 @@
       <c r="E96" s="13" t="n"/>
       <c r="F96" s="17" t="n"/>
       <c r="G96" s="13">
-        <f>IF(F96="","",IF(F96&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F96="","",IF(F96&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H96" s="15" t="n"/>
@@ -4139,7 +4139,7 @@
       <c r="E97" s="9" t="n"/>
       <c r="F97" s="16" t="n"/>
       <c r="G97" s="9">
-        <f>IF(F97="","",IF(F97&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F97="","",IF(F97&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H97" s="11" t="n"/>
@@ -4152,7 +4152,7 @@
       <c r="E98" s="13" t="n"/>
       <c r="F98" s="17" t="n"/>
       <c r="G98" s="13">
-        <f>IF(F98="","",IF(F98&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F98="","",IF(F98&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H98" s="15" t="n"/>
@@ -4165,7 +4165,7 @@
       <c r="E99" s="9" t="n"/>
       <c r="F99" s="16" t="n"/>
       <c r="G99" s="9">
-        <f>IF(F99="","",IF(F99&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F99="","",IF(F99&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H99" s="11" t="n"/>
@@ -4178,7 +4178,7 @@
       <c r="E100" s="13" t="n"/>
       <c r="F100" s="17" t="n"/>
       <c r="G100" s="13">
-        <f>IF(F100="","",IF(F100&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F100="","",IF(F100&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H100" s="15" t="n"/>
@@ -4191,7 +4191,7 @@
       <c r="E101" s="9" t="n"/>
       <c r="F101" s="16" t="n"/>
       <c r="G101" s="9">
-        <f>IF(F101="","",IF(F101&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F101="","",IF(F101&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H101" s="11" t="n"/>
@@ -4204,7 +4204,7 @@
       <c r="E102" s="13" t="n"/>
       <c r="F102" s="17" t="n"/>
       <c r="G102" s="13">
-        <f>IF(F102="","",IF(F102&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655 / acionar RT"))</f>
+        <f>IF(F102="","",IF(F102&gt;=Parametros!$B$7,"OK (&gt;= fck)","ALERTA: abaixo do fck - aplicar criterios NBR 12655:2022 / acionar RT"))</f>
         <v/>
       </c>
       <c r="H102" s="15" t="n"/>
@@ -4322,7 +4322,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Como usar: uma linha por caminhão no Recebimento (veredito automático a partir dos Parametros); uma linha por CP na aba CPs. A "situação" dos CPs é triagem de alerta — a aceitação definitiva segue os critérios estatísticos da NBR 12655, aplicados pelo responsável técnico.</t>
+          <t>Como usar: uma linha por caminhão no Recebimento (veredito automático a partir dos Parametros); uma linha por CP na aba CPs. A "situação" dos CPs é triagem de alerta — a aceitação definitiva segue os critérios estatísticos da NBR 12655:2022, aplicados pelo responsável técnico.</t>
         </is>
       </c>
     </row>
